--- a/results/soae/SOAE Results (rho=1.0, Flattop, BW=50Hz, Mode=phi)/SOAE N_xi Fitted Parameters (rho=1.0, Flattop, BW=50Hz, Mode=phi).xlsx
+++ b/results/soae/SOAE Results (rho=1.0, Flattop, BW=50Hz, Mode=phi)/SOAE N_xi Fitted Parameters (rho=1.0, Flattop, BW=50Hz, Mode=phi).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,45 +451,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Frequency (Rounded)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>N_xi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>N_xi_std</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>T_xi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>T_xi_std</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A_xi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>A_xi_std</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Decayed Xi</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Decayed Num Cycles</t>
         </is>
@@ -513,30 +518,33 @@
         <v>1235.467529296875</v>
       </c>
       <c r="E2" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F2" t="n">
         <v>18.306688261328</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.3690403859840584</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.01481761991085807</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.0002987050466588024</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.244989836296079</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.02952978343630936</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.0002007714665117075</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.03900226757369615</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>48.18603515625</v>
       </c>
     </row>
@@ -558,30 +566,33 @@
         <v>2153.3203125</v>
       </c>
       <c r="E3" t="n">
+        <v>2153</v>
+      </c>
+      <c r="F3" t="n">
         <v>25.29690994447969</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.595348441113101</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.01174786203317334</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.0002764792760543381</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1.167710898740214</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.03010231027599296</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.0002225317243756129</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.03</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>64.599609375</v>
       </c>
     </row>
@@ -603,30 +614,33 @@
         <v>3703.7109375</v>
       </c>
       <c r="E4" t="n">
+        <v>3704</v>
+      </c>
+      <c r="F4" t="n">
         <v>41.52810638076929</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.089157157938954</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.01121256682326313</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.0002940718582844195</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.144163427061289</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.02870813561319475</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.0003427227295027229</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.02700680272108844</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>100.025390625</v>
       </c>
     </row>
@@ -648,30 +662,33 @@
         <v>4500.439453125</v>
       </c>
       <c r="E5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F5" t="n">
         <v>41.23098554583742</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.8730723390149405</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.00916154655012803</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.0001939971303043972</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.8167438702948226</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.02165438032864245</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>5.204528376960088e-05</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.02600907029478458</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>117.05224609375</v>
       </c>
     </row>
@@ -693,30 +710,33 @@
         <v>966.302490234375</v>
       </c>
       <c r="E6" t="n">
+        <v>966</v>
+      </c>
+      <c r="F6" t="n">
         <v>11.16111458848785</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.2845045168068702</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.01155033201433719</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.000294425937718389</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1.03959466091058</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.03580911673450345</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.000121007859575912</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.03299319727891156</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>31.88140869140625</v>
       </c>
     </row>
@@ -735,34 +755,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3022.723388671875</v>
+        <v>3151.922607421875</v>
       </c>
       <c r="E7" t="n">
-        <v>32.85410002839859</v>
+        <v>3152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.991437602134656</v>
+        <v>30.40989913739679</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0108690395394843</v>
+        <v>0.8302988362606313</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003279948161483192</v>
+        <v>0.009648047533207253</v>
       </c>
       <c r="I7" t="n">
-        <v>1.062929278007326</v>
+        <v>0.0002634261495842301</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05328801022286783</v>
+        <v>1.094492102218201</v>
       </c>
       <c r="K7" t="n">
-        <v>8.314328915240177e-05</v>
+        <v>0.03294355000433496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03399092970521542</v>
+        <v>0.0001923642166464746</v>
       </c>
       <c r="M7" t="n">
-        <v>102.7451782226562</v>
+        <v>0.02399092970521542</v>
+      </c>
+      <c r="N7" t="n">
+        <v>75.6175537109375</v>
       </c>
     </row>
     <row r="8">
@@ -780,34 +803,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3151.922607421875</v>
+        <v>3954.034423828125</v>
       </c>
       <c r="E8" t="n">
-        <v>30.40989913739679</v>
+        <v>3954</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8302988362606313</v>
+        <v>31.86512210603134</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009648047533207253</v>
+        <v>0.5955162417458386</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002634261495842301</v>
+        <v>0.008058888388528725</v>
       </c>
       <c r="I8" t="n">
-        <v>1.094492102218201</v>
+        <v>0.0001506097767275596</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03294355000433496</v>
+        <v>0.8485684437948837</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001923642166464746</v>
+        <v>0.01568742471093194</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02399092970521542</v>
+        <v>6.257251609513855e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>75.6175537109375</v>
+        <v>0.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>79.0806884765625</v>
       </c>
     </row>
     <row r="9">
@@ -817,42 +843,45 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACsb4rearSOAEwf1.mat</t>
+          <t>ACsb24rearSOAEwfA1.mat</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3954.034423828125</v>
+        <v>2177.545166015625</v>
       </c>
       <c r="E9" t="n">
-        <v>31.86512210603134</v>
+        <v>2178</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5955162417458386</v>
+        <v>28.52641489875884</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008058888388528725</v>
+        <v>0.8644506715203875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001506097767275596</v>
+        <v>0.0131002632431984</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8485684437948837</v>
+        <v>0.0003969840373516205</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01568742471093194</v>
+        <v>1.259398907356392</v>
       </c>
       <c r="K9" t="n">
-        <v>6.257251609513855e-05</v>
+        <v>0.03694001935170459</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02</v>
+        <v>0.0006131002388727199</v>
       </c>
       <c r="M9" t="n">
-        <v>79.0806884765625</v>
+        <v>0.03099773242630385</v>
+      </c>
+      <c r="N9" t="n">
+        <v>67.49896240234375</v>
       </c>
     </row>
     <row r="10">
@@ -870,34 +899,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1811.480712890625</v>
+        <v>3111.5478515625</v>
       </c>
       <c r="E10" t="n">
-        <v>23.97310956875118</v>
+        <v>3112</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2823202957666863</v>
+        <v>29.68215229911629</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01323398554461929</v>
+        <v>0.4267803169559746</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001558505667533058</v>
+        <v>0.009539352667904833</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8390822319957771</v>
+        <v>0.0001371601329356584</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01603815453141878</v>
+        <v>1.056193478412823</v>
       </c>
       <c r="K10" t="n">
-        <v>1.20314767802092e-05</v>
+        <v>0.01554751289709087</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04299319727891156</v>
+        <v>6.473141480524591e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>77.88134765625</v>
+        <v>0.02399092970521542</v>
+      </c>
+      <c r="N10" t="n">
+        <v>74.64892578125</v>
       </c>
     </row>
     <row r="11">
@@ -915,34 +947,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2177.545166015625</v>
+        <v>3477.6123046875</v>
       </c>
       <c r="E11" t="n">
-        <v>28.52641489875884</v>
+        <v>3478</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8644506715203875</v>
+        <v>31.06055555179859</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0131002632431984</v>
+        <v>0.9146717045149659</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003969840373516205</v>
+        <v>0.008931575124096447</v>
       </c>
       <c r="I11" t="n">
-        <v>1.259398907356392</v>
+        <v>0.0002630171578591648</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03694001935170459</v>
+        <v>1.116934099595815</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0006131002388727199</v>
+        <v>0.03814322740928681</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03099773242630385</v>
+        <v>0.0002135071431182884</v>
       </c>
       <c r="M11" t="n">
-        <v>67.49896240234375</v>
+        <v>0.02399092970521542</v>
+      </c>
+      <c r="N11" t="n">
+        <v>83.43115234375</v>
       </c>
     </row>
     <row r="12">
@@ -952,42 +987,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACsb24rearSOAEwfA1.mat</t>
+          <t>ACsb30learSOAEwfA2.mat</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3111.5478515625</v>
+        <v>1798.0224609375</v>
       </c>
       <c r="E12" t="n">
-        <v>29.68215229911629</v>
+        <v>1798</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4267803169559746</v>
+        <v>19.97564891497187</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009539352667904833</v>
+        <v>0.6034139717733831</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0001371601329356584</v>
+        <v>0.01110978830851559</v>
       </c>
       <c r="I12" t="n">
-        <v>1.056193478412823</v>
+        <v>0.0003355986840446694</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01554751289709087</v>
+        <v>0.974712081647007</v>
       </c>
       <c r="K12" t="n">
-        <v>6.473141480524591e-05</v>
+        <v>0.03018685437935022</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02399092970521542</v>
+        <v>0.0002432732121475753</v>
       </c>
       <c r="M12" t="n">
-        <v>74.64892578125</v>
+        <v>0.02600907029478458</v>
+      </c>
+      <c r="N12" t="n">
+        <v>46.764892578125</v>
       </c>
     </row>
     <row r="13">
@@ -997,42 +1035,45 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ACsb24rearSOAEwfA1.mat</t>
+          <t>ACsb30learSOAEwfA2.mat</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3477.6123046875</v>
+        <v>2139.862060546875</v>
       </c>
       <c r="E13" t="n">
-        <v>31.06055555179859</v>
+        <v>2140</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9146717045149659</v>
+        <v>16.10257133355928</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008931575124096447</v>
+        <v>0.4154622733024121</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002630171578591648</v>
+        <v>0.007525051091117537</v>
       </c>
       <c r="I13" t="n">
-        <v>1.116934099595815</v>
+        <v>0.0001941537639095458</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03814322740928681</v>
+        <v>0.7013784437903158</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0002135071431182884</v>
+        <v>0.02065205830061842</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02399092970521542</v>
+        <v>5.43952414301807e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>83.43115234375</v>
+        <v>0.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>42.7972412109375</v>
       </c>
     </row>
     <row r="14">
@@ -1050,34 +1091,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1798.0224609375</v>
+        <v>2417.10205078125</v>
       </c>
       <c r="E14" t="n">
-        <v>19.97564891497187</v>
+        <v>2417</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6034139717733831</v>
+        <v>20.27253682937761</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01110978830851559</v>
+        <v>0.5366492113889888</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003355986840446694</v>
+        <v>0.008387124913830249</v>
       </c>
       <c r="I14" t="n">
-        <v>0.974712081647007</v>
+        <v>0.0002220217434408838</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03018685437935022</v>
+        <v>0.5896820563668638</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0002432732121475753</v>
+        <v>0.01678981563699513</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02600907029478458</v>
+        <v>4.925455955194371e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>46.764892578125</v>
+        <v>0.02099773242630385</v>
+      </c>
+      <c r="N14" t="n">
+        <v>50.753662109375</v>
       </c>
     </row>
     <row r="15">
@@ -1095,124 +1139,133 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2139.862060546875</v>
+        <v>2783.16650390625</v>
       </c>
       <c r="E15" t="n">
-        <v>16.10257133355928</v>
+        <v>2783</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4154622733024121</v>
+        <v>25.43828047953511</v>
       </c>
       <c r="G15" t="n">
-        <v>0.007525051091117537</v>
+        <v>1.144779192487545</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0001941537639095458</v>
+        <v>0.009140049811548031</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7013784437903158</v>
+        <v>0.0004113225676152744</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02065205830061842</v>
+        <v>0.5115609906061731</v>
       </c>
       <c r="K15" t="n">
-        <v>5.43952414301807e-05</v>
+        <v>0.02370136063912024</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02</v>
+        <v>0.000125193771606749</v>
       </c>
       <c r="M15" t="n">
-        <v>42.7972412109375</v>
+        <v>0.02199546485260771</v>
+      </c>
+      <c r="N15" t="n">
+        <v>61.217041015625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anole</t>
+          <t>Tokay</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACsb30learSOAEwfA2.mat</t>
+          <t>tokay_GG1rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2417.10205078125</v>
+        <v>1342.7734375</v>
       </c>
       <c r="E16" t="n">
-        <v>20.27253682937761</v>
+        <v>1343</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5366492113889888</v>
+        <v>10.69166059430503</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008387124913830249</v>
+        <v>0.1760964723817636</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002220217434408838</v>
+        <v>0.007962371235322438</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5896820563668638</v>
+        <v>0.0001311438456137643</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01678981563699513</v>
+        <v>0.7695268930878842</v>
       </c>
       <c r="K16" t="n">
-        <v>4.925455955194371e-05</v>
+        <v>0.0172105369211576</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02099773242630385</v>
+        <v>1.986000088344137e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>50.753662109375</v>
+        <v>0.024</v>
+      </c>
+      <c r="N16" t="n">
+        <v>32.22656249999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Anole</t>
+          <t>Tokay</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACsb30learSOAEwfA2.mat</t>
+          <t>tokay_GG1rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2783.16650390625</v>
+        <v>1779.1748046875</v>
       </c>
       <c r="E17" t="n">
-        <v>25.43828047953511</v>
+        <v>1779</v>
       </c>
       <c r="F17" t="n">
-        <v>1.144779192487545</v>
+        <v>17.32916630410013</v>
       </c>
       <c r="G17" t="n">
-        <v>0.009140049811548031</v>
+        <v>0.4232590709113763</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0004113225676152744</v>
+        <v>0.009740002083237621</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5115609906061731</v>
+        <v>0.000237896281914648</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02370136063912024</v>
+        <v>0.9570870177067973</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000125193771606749</v>
+        <v>0.03301417938806337</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02199546485260771</v>
+        <v>7.663130739317239e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>61.217041015625</v>
+        <v>0.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>53.37524414062499</v>
       </c>
     </row>
     <row r="18">
@@ -1230,34 +1283,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1342.7734375</v>
+        <v>3649.90234375</v>
       </c>
       <c r="E18" t="n">
-        <v>10.69166059430503</v>
+        <v>3650</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1760964723817636</v>
+        <v>33.75892247630429</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007962371235322438</v>
+        <v>1.028840650113268</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0001311438456137643</v>
+        <v>0.009249267321935947</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7695268930878842</v>
+        <v>0.0002818816924992607</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0172105369211576</v>
+        <v>0.7199080342510847</v>
       </c>
       <c r="K18" t="n">
-        <v>1.986000088344137e-05</v>
+        <v>0.02708342108361399</v>
       </c>
       <c r="L18" t="n">
-        <v>0.024</v>
+        <v>7.995199215624267e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>32.22656249999999</v>
+        <v>0.025</v>
+      </c>
+      <c r="N18" t="n">
+        <v>91.24755859375</v>
       </c>
     </row>
     <row r="19">
@@ -1275,34 +1331,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1779.1748046875</v>
+        <v>4211.425781249999</v>
       </c>
       <c r="E19" t="n">
-        <v>17.32916630410013</v>
+        <v>4211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4232590709113763</v>
+        <v>46.12704065170114</v>
       </c>
       <c r="G19" t="n">
-        <v>0.009740002083237621</v>
+        <v>1.075126454008817</v>
       </c>
       <c r="H19" t="n">
-        <v>0.000237896281914648</v>
+        <v>0.01095283237735466</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9570870177067973</v>
+        <v>0.0002552879974272531</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03301417938806337</v>
+        <v>1.12866937685471</v>
       </c>
       <c r="K19" t="n">
-        <v>7.663130739317239e-05</v>
+        <v>0.03671680144623923</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03</v>
+        <v>0.0001037269999680694</v>
       </c>
       <c r="M19" t="n">
-        <v>53.37524414062499</v>
+        <v>0.032</v>
+      </c>
+      <c r="N19" t="n">
+        <v>134.765625</v>
       </c>
     </row>
     <row r="20">
@@ -1312,42 +1371,45 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>tokay_GG1rearSOAEwf.mat</t>
+          <t>tokay_GG2rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3649.90234375</v>
+        <v>1364.1357421875</v>
       </c>
       <c r="E20" t="n">
-        <v>33.75892247630429</v>
+        <v>1364</v>
       </c>
       <c r="F20" t="n">
-        <v>1.028840650113268</v>
+        <v>11.17892505535753</v>
       </c>
       <c r="G20" t="n">
-        <v>0.009249267321935947</v>
+        <v>0.5165510225718823</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002818816924992607</v>
+        <v>0.008194877320222721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7199080342510847</v>
+        <v>0.0003786654118039249</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02708342108361399</v>
+        <v>0.6745621062333408</v>
       </c>
       <c r="K20" t="n">
-        <v>7.995199215624267e-05</v>
+        <v>0.04402790446511812</v>
       </c>
       <c r="L20" t="n">
-        <v>0.025</v>
+        <v>7.726461382615047e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>91.24755859375</v>
+        <v>0.022</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30.01098632812499</v>
       </c>
     </row>
     <row r="21">
@@ -1357,42 +1419,45 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tokay_GG1rearSOAEwf.mat</t>
+          <t>tokay_GG2rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4211.425781249999</v>
+        <v>1776.123046875</v>
       </c>
       <c r="E21" t="n">
-        <v>46.12704065170114</v>
+        <v>1776</v>
       </c>
       <c r="F21" t="n">
-        <v>1.075126454008817</v>
+        <v>15.89647682661615</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01095283237735466</v>
+        <v>0.7054151176192633</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0002552879974272531</v>
+        <v>0.008950098842861824</v>
       </c>
       <c r="I21" t="n">
-        <v>1.12866937685471</v>
+        <v>0.0003971656799681791</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03671680144623923</v>
+        <v>0.7173081035430412</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0001037269999680694</v>
+        <v>0.04246533504862162</v>
       </c>
       <c r="L21" t="n">
-        <v>0.032</v>
+        <v>0.0001014996746024675</v>
       </c>
       <c r="M21" t="n">
-        <v>134.765625</v>
+        <v>0.023</v>
+      </c>
+      <c r="N21" t="n">
+        <v>40.85083007812499</v>
       </c>
     </row>
     <row r="22">
@@ -1410,34 +1475,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1364.1357421875</v>
+        <v>3607.177734375</v>
       </c>
       <c r="E22" t="n">
-        <v>11.17892505535753</v>
+        <v>3607</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5165510225718823</v>
+        <v>37.73114265379662</v>
       </c>
       <c r="G22" t="n">
-        <v>0.008194877320222721</v>
+        <v>1.449612615928588</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0003786654118039249</v>
+        <v>0.01046001761827079</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6745621062333408</v>
+        <v>0.0004018689187711335</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04402790446511812</v>
+        <v>0.9157383972568074</v>
       </c>
       <c r="K22" t="n">
-        <v>7.726461382615047e-05</v>
+        <v>0.03712832976532102</v>
       </c>
       <c r="L22" t="n">
-        <v>0.022</v>
+        <v>0.0003092315633094102</v>
       </c>
       <c r="M22" t="n">
-        <v>30.01098632812499</v>
+        <v>0.025</v>
+      </c>
+      <c r="N22" t="n">
+        <v>90.179443359375</v>
       </c>
     </row>
     <row r="23">
@@ -1455,34 +1523,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1776.123046875</v>
+        <v>4394.531249999999</v>
       </c>
       <c r="E23" t="n">
-        <v>15.89647682661615</v>
+        <v>4395</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7054151176192633</v>
+        <v>40.65544364344527</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008950098842861824</v>
+        <v>1.63784606723683</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0003971656799681791</v>
+        <v>0.00925137206464177</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7173081035430412</v>
+        <v>0.0003727009717445588</v>
       </c>
       <c r="J23" t="n">
-        <v>0.04246533504862162</v>
+        <v>0.6583620360973251</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0001014996746024675</v>
+        <v>0.0297556066450585</v>
       </c>
       <c r="L23" t="n">
+        <v>0.0001351758422769943</v>
+      </c>
+      <c r="M23" t="n">
         <v>0.023</v>
       </c>
-      <c r="M23" t="n">
-        <v>40.85083007812499</v>
+      <c r="N23" t="n">
+        <v>101.07421875</v>
       </c>
     </row>
     <row r="24">
@@ -1492,42 +1563,45 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tokay_GG2rearSOAEwf.mat</t>
+          <t>tokay_GG3rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3607.177734375</v>
+        <v>1257.32421875</v>
       </c>
       <c r="E24" t="n">
-        <v>37.73114265379662</v>
+        <v>1257</v>
       </c>
       <c r="F24" t="n">
-        <v>1.449612615928588</v>
+        <v>14.32494353004988</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01046001761827079</v>
+        <v>0.5390601189704403</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0004018689187711335</v>
+        <v>0.01139319780564744</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9157383972568074</v>
+        <v>0.0004287359703500823</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03712832976532102</v>
+        <v>0.8770891908533835</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0003092315633094102</v>
+        <v>0.04174508411430886</v>
       </c>
       <c r="L24" t="n">
-        <v>0.025</v>
+        <v>0.0001964491379633126</v>
       </c>
       <c r="M24" t="n">
-        <v>90.179443359375</v>
+        <v>0.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>37.71972656249999</v>
       </c>
     </row>
     <row r="25">
@@ -1537,42 +1611,45 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tokay_GG2rearSOAEwf.mat</t>
+          <t>tokay_GG3rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4394.531249999999</v>
+        <v>2578.7353515625</v>
       </c>
       <c r="E25" t="n">
-        <v>40.65544364344527</v>
+        <v>2579</v>
       </c>
       <c r="F25" t="n">
-        <v>1.63784606723683</v>
+        <v>18.99626220687842</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00925137206464177</v>
+        <v>0.6072719896218819</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0003727009717445588</v>
+        <v>0.007366503195207008</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6583620360973251</v>
+        <v>0.0002354921722595246</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0297556066450585</v>
+        <v>0.8303156667294969</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0001351758422769943</v>
+        <v>0.04097745306654904</v>
       </c>
       <c r="L25" t="n">
+        <v>5.044628888431499e-05</v>
+      </c>
+      <c r="M25" t="n">
         <v>0.023</v>
       </c>
-      <c r="M25" t="n">
-        <v>101.07421875</v>
+      <c r="N25" t="n">
+        <v>59.31091308593749</v>
       </c>
     </row>
     <row r="26">
@@ -1590,34 +1667,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1257.32421875</v>
+        <v>3567.5048828125</v>
       </c>
       <c r="E26" t="n">
-        <v>14.32494353004988</v>
+        <v>3568</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5390601189704403</v>
+        <v>34.97447838578351</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01139319780564744</v>
+        <v>1.249344345561586</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0004287359703500823</v>
+        <v>0.009803624531611243</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8770891908533835</v>
+        <v>0.0003502011592417628</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04174508411430886</v>
+        <v>0.8817297569450167</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0001964491379633126</v>
+        <v>0.03434207674933716</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03</v>
+        <v>0.0002175897622740973</v>
       </c>
       <c r="M26" t="n">
-        <v>37.71972656249999</v>
+        <v>0.024</v>
+      </c>
+      <c r="N26" t="n">
+        <v>85.62011718749999</v>
       </c>
     </row>
     <row r="27">
@@ -1627,42 +1707,45 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tokay_GG3rearSOAEwf.mat</t>
+          <t>tokay_GG4rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1837.158203125</v>
+        <v>1251.220703125</v>
       </c>
       <c r="E27" t="n">
-        <v>13.69192523662817</v>
+        <v>1251</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6034139080106731</v>
+        <v>13.65795908537932</v>
       </c>
       <c r="G27" t="n">
-        <v>0.007452774188601861</v>
+        <v>0.5145027674971088</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0003284496169052116</v>
+        <v>0.0109157073977978</v>
       </c>
       <c r="I27" t="n">
-        <v>0.706938380258768</v>
+        <v>0.0004112006508620796</v>
       </c>
       <c r="J27" t="n">
-        <v>0.04688690934595412</v>
+        <v>1.002510682548067</v>
       </c>
       <c r="K27" t="n">
-        <v>5.914898884343351e-05</v>
+        <v>0.04889588957124038</v>
       </c>
       <c r="L27" t="n">
-        <v>0.021</v>
+        <v>0.0002279447290236955</v>
       </c>
       <c r="M27" t="n">
-        <v>38.580322265625</v>
+        <v>0.029</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36.28540039062499</v>
       </c>
     </row>
     <row r="28">
@@ -1672,42 +1755,45 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>tokay_GG3rearSOAEwf.mat</t>
+          <t>tokay_GG4rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2578.7353515625</v>
+        <v>2590.9423828125</v>
       </c>
       <c r="E28" t="n">
-        <v>18.99626220687842</v>
+        <v>2591</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6072719896218819</v>
+        <v>24.41431871821503</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007366503195207008</v>
+        <v>0.8301093520243699</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0002354921722595246</v>
+        <v>0.009422949302219909</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8303156667294969</v>
+        <v>0.0003203889663973446</v>
       </c>
       <c r="J28" t="n">
-        <v>0.04097745306654904</v>
+        <v>0.8328716851602599</v>
       </c>
       <c r="K28" t="n">
-        <v>5.044628888431499e-05</v>
+        <v>0.03451331485304102</v>
       </c>
       <c r="L28" t="n">
-        <v>0.023</v>
+        <v>0.0001365347929539875</v>
       </c>
       <c r="M28" t="n">
-        <v>59.31091308593749</v>
+        <v>0.025</v>
+      </c>
+      <c r="N28" t="n">
+        <v>64.77355957031249</v>
       </c>
     </row>
     <row r="29">
@@ -1717,42 +1803,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tokay_GG3rearSOAEwf.mat</t>
+          <t>tokay_GG4rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3567.5048828125</v>
+        <v>3216.552734375</v>
       </c>
       <c r="E29" t="n">
-        <v>34.97447838578351</v>
+        <v>3217</v>
       </c>
       <c r="F29" t="n">
-        <v>1.249344345561586</v>
+        <v>29.62648422299942</v>
       </c>
       <c r="G29" t="n">
-        <v>0.009803624531611243</v>
+        <v>1.131505733697491</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0003502011592417628</v>
+        <v>0.009210632210808778</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8817297569450167</v>
+        <v>0.0003517759002068254</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03434207674933716</v>
+        <v>0.6740010612060136</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0002175897622740973</v>
+        <v>0.03159363569920032</v>
       </c>
       <c r="L29" t="n">
+        <v>0.0001020011721056376</v>
+      </c>
+      <c r="M29" t="n">
         <v>0.024</v>
       </c>
-      <c r="M29" t="n">
-        <v>85.62011718749999</v>
+      <c r="N29" t="n">
+        <v>77.19726562499999</v>
       </c>
     </row>
     <row r="30">
@@ -1770,169 +1859,181 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1251.220703125</v>
+        <v>3582.763671875</v>
       </c>
       <c r="E30" t="n">
-        <v>13.65795908537932</v>
+        <v>3583</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5145027674971088</v>
+        <v>34.52374034953</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0109157073977978</v>
+        <v>1.415655296318656</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0004112006508620796</v>
+        <v>0.009636064086655871</v>
       </c>
       <c r="I30" t="n">
-        <v>1.002510682548067</v>
+        <v>0.0003951294101343249</v>
       </c>
       <c r="J30" t="n">
-        <v>0.04889588957124038</v>
+        <v>0.7348881400323389</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0002279447290236955</v>
+        <v>0.02998586396090274</v>
       </c>
       <c r="L30" t="n">
-        <v>0.029</v>
+        <v>0.0002236340154518327</v>
       </c>
       <c r="M30" t="n">
-        <v>36.28540039062499</v>
+        <v>0.022</v>
+      </c>
+      <c r="N30" t="n">
+        <v>78.82080078124999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tokay</t>
+          <t>Owl</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>tokay_GG4rearSOAEwf.mat</t>
+          <t>Owl2R1.mat</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2590.9423828125</v>
+        <v>4350.5859375</v>
       </c>
       <c r="E31" t="n">
-        <v>24.41431871821503</v>
+        <v>4351</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8301093520243699</v>
+        <v>38.18817150603999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.009422949302219909</v>
+        <v>2.062741876737991</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0003203889663973446</v>
+        <v>0.008777707659300775</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8328716851602599</v>
+        <v>0.0004741296704331543</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03451331485304102</v>
+        <v>0.4666897477044611</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0001365347929539875</v>
+        <v>0.02632494419016262</v>
       </c>
       <c r="L31" t="n">
-        <v>0.025</v>
+        <v>0.0001339445586304853</v>
       </c>
       <c r="M31" t="n">
-        <v>64.77355957031249</v>
+        <v>0.021</v>
+      </c>
+      <c r="N31" t="n">
+        <v>91.3623046875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tokay</t>
+          <t>Owl</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tokay_GG4rearSOAEwf.mat</t>
+          <t>Owl2R1.mat</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3216.552734375</v>
+        <v>7453.125</v>
       </c>
       <c r="E32" t="n">
-        <v>29.62648422299942</v>
+        <v>7453</v>
       </c>
       <c r="F32" t="n">
-        <v>1.131505733697491</v>
+        <v>69.19801128502411</v>
       </c>
       <c r="G32" t="n">
-        <v>0.009210632210808778</v>
+        <v>1.29562100210892</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0003517759002068254</v>
+        <v>0.009284429187089188</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6740010612060136</v>
+        <v>0.0001738359415827481</v>
       </c>
       <c r="J32" t="n">
-        <v>0.03159363569920032</v>
+        <v>0.5678163655099446</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0001020011721056376</v>
+        <v>0.01095659896956142</v>
       </c>
       <c r="L32" t="n">
-        <v>0.024</v>
+        <v>2.903193464227278e-05</v>
       </c>
       <c r="M32" t="n">
-        <v>77.19726562499999</v>
+        <v>0.023</v>
+      </c>
+      <c r="N32" t="n">
+        <v>171.421875</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tokay</t>
+          <t>Owl</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tokay_GG4rearSOAEwf.mat</t>
+          <t>Owl2R1.mat</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3582.763671875</v>
+        <v>8452.1484375</v>
       </c>
       <c r="E33" t="n">
-        <v>34.52374034953</v>
+        <v>8452</v>
       </c>
       <c r="F33" t="n">
-        <v>1.415655296318656</v>
+        <v>69.4790088667789</v>
       </c>
       <c r="G33" t="n">
-        <v>0.009636064086655871</v>
+        <v>1.153285808860182</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003951294101343249</v>
+        <v>0.008220277883256105</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7348881400323389</v>
+        <v>0.000136448835155728</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02998586396090274</v>
+        <v>0.6154222216427551</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0002236340154518327</v>
+        <v>0.008877207013722566</v>
       </c>
       <c r="L33" t="n">
-        <v>0.022</v>
+        <v>3.359224672051262e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>78.82080078124999</v>
+        <v>0.019</v>
+      </c>
+      <c r="N33" t="n">
+        <v>160.5908203125</v>
       </c>
     </row>
     <row r="34">
@@ -1950,34 +2051,37 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4350.5859375</v>
+        <v>9026.3671875</v>
       </c>
       <c r="E34" t="n">
-        <v>38.18817150603999</v>
+        <v>9026</v>
       </c>
       <c r="F34" t="n">
-        <v>2.062741876737991</v>
+        <v>81.38665497811712</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008777707659300775</v>
+        <v>2.179639449356527</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0004741296704331543</v>
+        <v>0.00901654600211965</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4666897477044611</v>
+        <v>0.0002414747155838022</v>
       </c>
       <c r="J34" t="n">
-        <v>0.02632494419016262</v>
+        <v>0.721227100608454</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0001339445586304853</v>
+        <v>0.01785733306857111</v>
       </c>
       <c r="L34" t="n">
-        <v>0.021</v>
+        <v>0.0001004126253638873</v>
       </c>
       <c r="M34" t="n">
-        <v>91.3623046875</v>
+        <v>0.02</v>
+      </c>
+      <c r="N34" t="n">
+        <v>180.52734375</v>
       </c>
     </row>
     <row r="35">
@@ -1987,42 +2091,45 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Owl2R1.mat</t>
+          <t>Owl7L1.mat</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7453.125</v>
+        <v>6837.890625</v>
       </c>
       <c r="E35" t="n">
-        <v>69.19801128502411</v>
+        <v>6838</v>
       </c>
       <c r="F35" t="n">
-        <v>1.29562100210892</v>
+        <v>61.14423462696202</v>
       </c>
       <c r="G35" t="n">
-        <v>0.009284429187089188</v>
+        <v>2.43283311556865</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0001738359415827481</v>
+        <v>0.008941973187376337</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5678163655099446</v>
+        <v>0.000355787076598443</v>
       </c>
       <c r="J35" t="n">
-        <v>0.01095659896956142</v>
+        <v>0.5542966708632717</v>
       </c>
       <c r="K35" t="n">
-        <v>2.903193464227278e-05</v>
+        <v>0.02302424109636626</v>
       </c>
       <c r="L35" t="n">
-        <v>0.023</v>
+        <v>0.0001126053621516931</v>
       </c>
       <c r="M35" t="n">
-        <v>171.421875</v>
+        <v>0.022</v>
+      </c>
+      <c r="N35" t="n">
+        <v>150.43359375</v>
       </c>
     </row>
     <row r="36">
@@ -2032,42 +2139,45 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Owl2R1.mat</t>
+          <t>Owl7L1.mat</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8452.1484375</v>
+        <v>7901.3671875</v>
       </c>
       <c r="E36" t="n">
-        <v>69.4790088667789</v>
+        <v>7901</v>
       </c>
       <c r="F36" t="n">
-        <v>1.153285808860182</v>
+        <v>72.61693277193591</v>
       </c>
       <c r="G36" t="n">
-        <v>0.008220277883256105</v>
+        <v>2.621698804344461</v>
       </c>
       <c r="H36" t="n">
-        <v>0.000136448835155728</v>
+        <v>0.009190426295694274</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6154222216427551</v>
+        <v>0.0003318031857185426</v>
       </c>
       <c r="J36" t="n">
-        <v>0.008877207013722566</v>
+        <v>0.7176820945998618</v>
       </c>
       <c r="K36" t="n">
-        <v>3.359224672051262e-05</v>
+        <v>0.02887872450328945</v>
       </c>
       <c r="L36" t="n">
-        <v>0.019</v>
+        <v>0.0001181910140158244</v>
       </c>
       <c r="M36" t="n">
-        <v>160.5908203125</v>
+        <v>0.022</v>
+      </c>
+      <c r="N36" t="n">
+        <v>173.830078125</v>
       </c>
     </row>
     <row r="37">
@@ -2077,42 +2187,45 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Owl2R1.mat</t>
+          <t>Owl7L1.mat</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9026.3671875</v>
+        <v>8835.9375</v>
       </c>
       <c r="E37" t="n">
-        <v>81.38665497811712</v>
+        <v>8836</v>
       </c>
       <c r="F37" t="n">
-        <v>2.179639449356527</v>
+        <v>75.33983965195233</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00901654600211965</v>
+        <v>2.557140366460105</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0002414747155838022</v>
+        <v>0.008526524735145799</v>
       </c>
       <c r="I37" t="n">
-        <v>0.721227100608454</v>
+        <v>0.0002894022695905335</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01785733306857111</v>
+        <v>0.7128489007584123</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0001004126253638873</v>
+        <v>0.02314669123347024</v>
       </c>
       <c r="L37" t="n">
+        <v>0.0001519252691792823</v>
+      </c>
+      <c r="M37" t="n">
         <v>0.02</v>
       </c>
-      <c r="M37" t="n">
-        <v>180.52734375</v>
+      <c r="N37" t="n">
+        <v>176.71875</v>
       </c>
     </row>
     <row r="38">
@@ -2130,34 +2243,37 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6837.890625</v>
+        <v>9257.8125</v>
       </c>
       <c r="E38" t="n">
-        <v>61.14423462696202</v>
+        <v>9258</v>
       </c>
       <c r="F38" t="n">
-        <v>2.43283311556865</v>
+        <v>89.1534077998639</v>
       </c>
       <c r="G38" t="n">
-        <v>0.008941973187376337</v>
+        <v>3.259690495762425</v>
       </c>
       <c r="H38" t="n">
-        <v>0.000355787076598443</v>
+        <v>0.009630072741251121</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5542966708632717</v>
+        <v>0.0003521015894156881</v>
       </c>
       <c r="J38" t="n">
-        <v>0.02302424109636626</v>
+        <v>0.3687694104084971</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0001126053621516931</v>
+        <v>0.01107179803851206</v>
       </c>
       <c r="L38" t="n">
-        <v>0.022</v>
+        <v>7.302487491588827e-05</v>
       </c>
       <c r="M38" t="n">
-        <v>150.43359375</v>
+        <v>0.021</v>
+      </c>
+      <c r="N38" t="n">
+        <v>194.4140625</v>
       </c>
     </row>
     <row r="39">
@@ -2167,42 +2283,45 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Owl7L1.mat</t>
+          <t>TAG6rearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7901.3671875</v>
+        <v>5625.54931640625</v>
       </c>
       <c r="E39" t="n">
-        <v>72.61693277193591</v>
+        <v>5626</v>
       </c>
       <c r="F39" t="n">
-        <v>2.621698804344461</v>
+        <v>51.83701769448351</v>
       </c>
       <c r="G39" t="n">
-        <v>0.009190426295694274</v>
+        <v>2.526739557456056</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0003318031857185426</v>
+        <v>0.009214569952005749</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7176820945998618</v>
+        <v>0.0004491542808250064</v>
       </c>
       <c r="J39" t="n">
-        <v>0.02887872450328945</v>
+        <v>0.7835877415703257</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0001181910140158244</v>
+        <v>0.04687451605713499</v>
       </c>
       <c r="L39" t="n">
-        <v>0.022</v>
+        <v>0.0002243659335072323</v>
       </c>
       <c r="M39" t="n">
-        <v>173.830078125</v>
+        <v>0.02399092970521542</v>
+      </c>
+      <c r="N39" t="n">
+        <v>134.962158203125</v>
       </c>
     </row>
     <row r="40">
@@ -2212,42 +2331,45 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owl7L1.mat</t>
+          <t>TAG6rearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8835.9375</v>
+        <v>8096.484375</v>
       </c>
       <c r="E40" t="n">
-        <v>75.33983965195233</v>
+        <v>8096</v>
       </c>
       <c r="F40" t="n">
-        <v>2.557140366460105</v>
+        <v>78.28887462547326</v>
       </c>
       <c r="G40" t="n">
-        <v>0.008526524735145799</v>
+        <v>2.624205836221664</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0002894022695905335</v>
+        <v>0.009669489990891665</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7128489007584123</v>
+        <v>0.0003241167048163005</v>
       </c>
       <c r="J40" t="n">
-        <v>0.02314669123347024</v>
+        <v>0.606666242649432</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0001519252691792823</v>
+        <v>0.02019008849351071</v>
       </c>
       <c r="L40" t="n">
-        <v>0.02</v>
+        <v>0.0001021461108885125</v>
       </c>
       <c r="M40" t="n">
-        <v>176.71875</v>
+        <v>0.02199546485260771</v>
+      </c>
+      <c r="N40" t="n">
+        <v>178.0859375</v>
       </c>
     </row>
     <row r="41">
@@ -2257,42 +2379,45 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Owl7L1.mat</t>
+          <t>TAG6rearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9257.8125</v>
+        <v>8489.46533203125</v>
       </c>
       <c r="E41" t="n">
-        <v>89.1534077998639</v>
+        <v>8489</v>
       </c>
       <c r="F41" t="n">
-        <v>3.259690495762425</v>
+        <v>101.9184343584824</v>
       </c>
       <c r="G41" t="n">
-        <v>0.009630072741251121</v>
+        <v>3.481792421635467</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0003521015894156881</v>
+        <v>0.01200528306228405</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3687694104084971</v>
+        <v>0.0004101309429344697</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01107179803851206</v>
+        <v>0.941342888221613</v>
       </c>
       <c r="K41" t="n">
-        <v>7.302487491588827e-05</v>
+        <v>0.03199093798015184</v>
       </c>
       <c r="L41" t="n">
-        <v>0.021</v>
+        <v>0.0003485549518335093</v>
       </c>
       <c r="M41" t="n">
-        <v>194.4140625</v>
+        <v>0.02800453514739229</v>
+      </c>
+      <c r="N41" t="n">
+        <v>237.7435302734375</v>
       </c>
     </row>
     <row r="42">
@@ -2310,34 +2435,37 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5625.54931640625</v>
+        <v>9864.898681640625</v>
       </c>
       <c r="E42" t="n">
-        <v>51.83701769448351</v>
+        <v>9865</v>
       </c>
       <c r="F42" t="n">
-        <v>2.526739557456056</v>
+        <v>92.57374287449112</v>
       </c>
       <c r="G42" t="n">
-        <v>0.009214569952005749</v>
+        <v>3.26948592510969</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0004491542808250064</v>
+        <v>0.009384155464949513</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7835877415703257</v>
+        <v>0.0003314262042239185</v>
       </c>
       <c r="J42" t="n">
-        <v>0.04687451605713499</v>
+        <v>0.6031090155337008</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0002243659335072323</v>
+        <v>0.02156217105194045</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02399092970521542</v>
+        <v>0.0001095498729547878</v>
       </c>
       <c r="M42" t="n">
-        <v>134.962158203125</v>
+        <v>0.02199546485260771</v>
+      </c>
+      <c r="N42" t="n">
+        <v>216.9830322265625</v>
       </c>
     </row>
     <row r="43">
@@ -2347,42 +2475,45 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TAG6rearSOAEwf1.mat</t>
+          <t>owl_TAG4learSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8096.484375</v>
+        <v>4944.561767578125</v>
       </c>
       <c r="E43" t="n">
-        <v>78.28887462547326</v>
+        <v>4945</v>
       </c>
       <c r="F43" t="n">
-        <v>2.624205836221664</v>
+        <v>45.28841458447616</v>
       </c>
       <c r="G43" t="n">
-        <v>0.009669489990891665</v>
+        <v>1.798293050157823</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0003241167048163005</v>
+        <v>0.009159237302168175</v>
       </c>
       <c r="I43" t="n">
-        <v>0.606666242649432</v>
+        <v>0.0003636910882475713</v>
       </c>
       <c r="J43" t="n">
-        <v>0.02019008849351071</v>
+        <v>0.5391445149782679</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0001021461108885125</v>
+        <v>0.02201095677423928</v>
       </c>
       <c r="L43" t="n">
+        <v>0.0001084582128997591</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.02199546485260771</v>
       </c>
-      <c r="M43" t="n">
-        <v>178.0859375</v>
+      <c r="N43" t="n">
+        <v>108.7579345703125</v>
       </c>
     </row>
     <row r="44">
@@ -2392,42 +2523,45 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TAG6rearSOAEwf1.mat</t>
+          <t>owl_TAG4learSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8489.46533203125</v>
+        <v>5768.206787109375</v>
       </c>
       <c r="E44" t="n">
-        <v>101.9184343584824</v>
+        <v>5768</v>
       </c>
       <c r="F44" t="n">
-        <v>3.481792421635467</v>
+        <v>68.8618131122638</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01200528306228405</v>
+        <v>2.105416667748536</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0004101309429344697</v>
+        <v>0.01193816651409832</v>
       </c>
       <c r="I44" t="n">
-        <v>0.941342888221613</v>
+        <v>0.0003650036736639992</v>
       </c>
       <c r="J44" t="n">
-        <v>0.03199093798015184</v>
+        <v>0.9243709592246925</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0003485549518335093</v>
+        <v>0.03284198698865044</v>
       </c>
       <c r="L44" t="n">
-        <v>0.02800453514739229</v>
+        <v>0.0002025271991541933</v>
       </c>
       <c r="M44" t="n">
-        <v>237.7435302734375</v>
+        <v>0.03099773242630385</v>
+      </c>
+      <c r="N44" t="n">
+        <v>178.8013305664062</v>
       </c>
     </row>
     <row r="45">
@@ -2437,42 +2571,45 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TAG6rearSOAEwf1.mat</t>
+          <t>owl_TAG4learSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9864.898681640625</v>
+        <v>7184.014892578125</v>
       </c>
       <c r="E45" t="n">
-        <v>92.57374287449112</v>
+        <v>7184</v>
       </c>
       <c r="F45" t="n">
-        <v>3.26948592510969</v>
+        <v>215.212239384061</v>
       </c>
       <c r="G45" t="n">
-        <v>0.009384155464949513</v>
+        <v>3.426336935219513</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0003314262042239185</v>
+        <v>0.02995709816893599</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6031090155337008</v>
+        <v>0.0004769390078463361</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02156217105194045</v>
+        <v>1.272598354498129</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0001095498729547878</v>
+        <v>0.01906358170377451</v>
       </c>
       <c r="L45" t="n">
-        <v>0.02199546485260771</v>
+        <v>0.0004631125362880487</v>
       </c>
       <c r="M45" t="n">
-        <v>216.9830322265625</v>
+        <v>0.07099773242630386</v>
+      </c>
+      <c r="N45" t="n">
+        <v>510.0487670898438</v>
       </c>
     </row>
     <row r="46">
@@ -2490,169 +2627,181 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4944.561767578125</v>
+        <v>9633.416748046875</v>
       </c>
       <c r="E46" t="n">
-        <v>45.28841458447616</v>
+        <v>9633</v>
       </c>
       <c r="F46" t="n">
-        <v>1.798293050157823</v>
+        <v>163.3124452650469</v>
       </c>
       <c r="G46" t="n">
-        <v>0.009159237302168175</v>
+        <v>3.053847747422519</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0003636910882475713</v>
+        <v>0.01695270219656568</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5391445149782679</v>
+        <v>0.0003170056717458705</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02201095677423928</v>
+        <v>1.103992840979661</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0001084582128997591</v>
+        <v>0.01949410344315334</v>
       </c>
       <c r="L46" t="n">
-        <v>0.02199546485260771</v>
+        <v>0.0002697444831906281</v>
       </c>
       <c r="M46" t="n">
-        <v>108.7579345703125</v>
+        <v>0.04099773242630386</v>
+      </c>
+      <c r="N46" t="n">
+        <v>394.9482421875</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>owl_TAG4learSOAEwf1.mat</t>
+          <t>ALrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5768.206787109375</v>
+        <v>2804.69970703125</v>
       </c>
       <c r="E47" t="n">
-        <v>68.8618131122638</v>
+        <v>2805</v>
       </c>
       <c r="F47" t="n">
-        <v>2.105416667748536</v>
+        <v>166.6900920782989</v>
       </c>
       <c r="G47" t="n">
-        <v>0.01193816651409832</v>
+        <v>0.8492322260921169</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0003650036736639992</v>
+        <v>0.05943242039795372</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9243709592246925</v>
+        <v>0.0003027890023174787</v>
       </c>
       <c r="J47" t="n">
-        <v>0.03284198698865044</v>
+        <v>0.5528739848972855</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0002025271991541933</v>
+        <v>0.002612825663191421</v>
       </c>
       <c r="L47" t="n">
-        <v>0.03099773242630385</v>
+        <v>2.192997217609307e-05</v>
       </c>
       <c r="M47" t="n">
-        <v>178.8013305664062</v>
+        <v>0.1529931972789116</v>
+      </c>
+      <c r="N47" t="n">
+        <v>429.0999755859375</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>owl_TAG4learSOAEwf1.mat</t>
+          <t>ALrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7184.014892578125</v>
+        <v>2941.973876953125</v>
       </c>
       <c r="E48" t="n">
-        <v>215.212239384061</v>
+        <v>2942</v>
       </c>
       <c r="F48" t="n">
-        <v>3.426336935219513</v>
+        <v>228.0762756117064</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02995709816893599</v>
+        <v>0.8233641777035026</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0004769390078463361</v>
+        <v>0.07752491529527623</v>
       </c>
       <c r="I48" t="n">
-        <v>1.272598354498129</v>
+        <v>0.0002798679431362678</v>
       </c>
       <c r="J48" t="n">
-        <v>0.01906358170377451</v>
+        <v>0.7447644131313451</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0004631125362880487</v>
+        <v>0.002386978485109103</v>
       </c>
       <c r="L48" t="n">
-        <v>0.07099773242630386</v>
+        <v>2.797789321411132e-05</v>
       </c>
       <c r="M48" t="n">
-        <v>510.0487670898438</v>
+        <v>0.1929931972789116</v>
+      </c>
+      <c r="N48" t="n">
+        <v>567.7809448242188</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>owl_TAG4learSOAEwf1.mat</t>
+          <t>ALrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9633.416748046875</v>
+        <v>3862.518310546875</v>
       </c>
       <c r="E49" t="n">
-        <v>163.3124452650469</v>
+        <v>3863</v>
       </c>
       <c r="F49" t="n">
-        <v>3.053847747422519</v>
+        <v>372.3006934282687</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01695270219656568</v>
+        <v>2.1663623000178</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0003170056717458705</v>
+        <v>0.09638807210613753</v>
       </c>
       <c r="I49" t="n">
-        <v>1.103992840979661</v>
+        <v>0.0005608678395394002</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01949410344315334</v>
+        <v>0.785571511370368</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0002697444831906281</v>
+        <v>0.004094832774943185</v>
       </c>
       <c r="L49" t="n">
-        <v>0.04099773242630386</v>
+        <v>0.000117809494576576</v>
       </c>
       <c r="M49" t="n">
-        <v>394.9482421875</v>
+        <v>0.2739909297052154</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1058.294982910156</v>
       </c>
     </row>
     <row r="50">
@@ -2662,42 +2811,45 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2662.042236328125</v>
+        <v>2339.044189453125</v>
       </c>
       <c r="E50" t="n">
-        <v>45.19298222584217</v>
+        <v>2339</v>
       </c>
       <c r="F50" t="n">
-        <v>1.405715733439253</v>
+        <v>815.7066563809069</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01697680886092134</v>
+        <v>2.810550591881639</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0005280591398047164</v>
+        <v>0.3487350346175467</v>
       </c>
       <c r="I50" t="n">
-        <v>0.512549776424676</v>
+        <v>0.001201580801489156</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02010324701979433</v>
+        <v>1.158221122438415</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0001189826116641344</v>
+        <v>0.003269391793929353</v>
       </c>
       <c r="L50" t="n">
-        <v>0.06099773242630385</v>
+        <v>0.0003078683878632456</v>
       </c>
       <c r="M50" t="n">
-        <v>162.3785400390625</v>
+        <v>0.8070068027210885</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1887.624572753906</v>
       </c>
     </row>
     <row r="51">
@@ -2707,42 +2859,45 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2804.69970703125</v>
+        <v>4050.933837890625</v>
       </c>
       <c r="E51" t="n">
-        <v>166.6900920782989</v>
+        <v>4051</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8492322260921169</v>
+        <v>831.8611357636494</v>
       </c>
       <c r="G51" t="n">
-        <v>0.05943242039795372</v>
+        <v>1.551520702691254</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0003027890023174787</v>
+        <v>0.2053504621533909</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5528739848972855</v>
+        <v>0.0003830032196969062</v>
       </c>
       <c r="J51" t="n">
-        <v>0.002612825663191421</v>
+        <v>1.035867697888161</v>
       </c>
       <c r="K51" t="n">
-        <v>2.192997217609307e-05</v>
+        <v>0.001785815282442076</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1529931972789116</v>
+        <v>3.581083538317358e-05</v>
       </c>
       <c r="M51" t="n">
-        <v>429.0999755859375</v>
+        <v>0.5219954648526077</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2114.569091796875</v>
       </c>
     </row>
     <row r="52">
@@ -2752,42 +2907,45 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2941.973876953125</v>
+        <v>5838.189697265625</v>
       </c>
       <c r="E52" t="n">
-        <v>228.0762756117064</v>
+        <v>5838</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8233641777035026</v>
+        <v>559.9452586154435</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07752491529527623</v>
+        <v>1.30158363423253</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0002798679431362678</v>
+        <v>0.09591076817488468</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7447644131313451</v>
+        <v>0.0002229430185939555</v>
       </c>
       <c r="J52" t="n">
-        <v>0.002386978485109103</v>
+        <v>0.8541515261468096</v>
       </c>
       <c r="K52" t="n">
-        <v>2.797789321411132e-05</v>
+        <v>0.001768645965736201</v>
       </c>
       <c r="L52" t="n">
-        <v>0.1929931972789116</v>
+        <v>1.866562863105081e-05</v>
       </c>
       <c r="M52" t="n">
-        <v>567.7809448242188</v>
+        <v>0.2380045351473923</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1389.515625</v>
       </c>
     </row>
     <row r="53">
@@ -2797,42 +2955,45 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3862.518310546875</v>
+        <v>8309.124755859375</v>
       </c>
       <c r="E53" t="n">
-        <v>372.3006934282687</v>
+        <v>8309</v>
       </c>
       <c r="F53" t="n">
-        <v>2.1663623000178</v>
+        <v>1473.649243969836</v>
       </c>
       <c r="G53" t="n">
-        <v>0.09638807210613753</v>
+        <v>6.188673143888594</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0005608678395394002</v>
+        <v>0.1773531253012728</v>
       </c>
       <c r="I53" t="n">
-        <v>0.785571511370368</v>
+        <v>0.0007448044560318469</v>
       </c>
       <c r="J53" t="n">
-        <v>0.004094832774943185</v>
+        <v>1.012256512012363</v>
       </c>
       <c r="K53" t="n">
-        <v>0.000117809494576576</v>
+        <v>0.003366944908550142</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2739909297052154</v>
+        <v>0.0002343120579684908</v>
       </c>
       <c r="M53" t="n">
-        <v>1058.294982910156</v>
+        <v>0.47</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3905.288635253906</v>
       </c>
     </row>
     <row r="54">
@@ -2842,42 +3003,45 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2339.044189453125</v>
+        <v>732.12890625</v>
       </c>
       <c r="E54" t="n">
-        <v>815.7066563809069</v>
+        <v>732</v>
       </c>
       <c r="F54" t="n">
-        <v>2.810550591881639</v>
+        <v>431.1704675750619</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3487350346175467</v>
+        <v>1.367336064577971</v>
       </c>
       <c r="H54" t="n">
-        <v>0.001201580801489156</v>
+        <v>0.58892698252216</v>
       </c>
       <c r="I54" t="n">
-        <v>1.158221122438415</v>
+        <v>0.001867616553458507</v>
       </c>
       <c r="J54" t="n">
-        <v>0.003269391793929353</v>
+        <v>0.5639010890242845</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0003078683878632456</v>
+        <v>0.001380781937940807</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8070068027210885</v>
+        <v>9.159737506708837e-05</v>
       </c>
       <c r="M54" t="n">
-        <v>1887.624572753906</v>
+        <v>1.177006802721088</v>
+      </c>
+      <c r="N54" t="n">
+        <v>861.720703125</v>
       </c>
     </row>
     <row r="55">
@@ -2887,42 +3051,45 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4050.933837890625</v>
+        <v>985.14404296875</v>
       </c>
       <c r="E55" t="n">
-        <v>831.8611357636494</v>
+        <v>985</v>
       </c>
       <c r="F55" t="n">
-        <v>1.551520702691254</v>
+        <v>709.1199832076535</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2053504621533909</v>
+        <v>3.402689580214135</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0003830032196969062</v>
+        <v>0.7198135016588104</v>
       </c>
       <c r="I55" t="n">
-        <v>1.035867697888161</v>
+        <v>0.003454002086801506</v>
       </c>
       <c r="J55" t="n">
-        <v>0.001785815282442076</v>
+        <v>0.4873676662189558</v>
       </c>
       <c r="K55" t="n">
-        <v>3.581083538317358e-05</v>
+        <v>0.001619950741801077</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5219954648526077</v>
+        <v>0.0002302671668819459</v>
       </c>
       <c r="M55" t="n">
-        <v>2114.569091796875</v>
+        <v>1.368004535147392</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1347.681518554688</v>
       </c>
     </row>
     <row r="56">
@@ -2932,42 +3099,45 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5838.189697265625</v>
+        <v>1633.831787109375</v>
       </c>
       <c r="E56" t="n">
-        <v>559.9452586154435</v>
+        <v>1634</v>
       </c>
       <c r="F56" t="n">
-        <v>1.30158363423253</v>
+        <v>135.2652096623919</v>
       </c>
       <c r="G56" t="n">
-        <v>0.09591076817488468</v>
+        <v>1.034008662370157</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0002229430185939555</v>
+        <v>0.08279016893269485</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8541515261468096</v>
+        <v>0.0006328733903503964</v>
       </c>
       <c r="J56" t="n">
-        <v>0.001768645965736201</v>
+        <v>0.4136555602514778</v>
       </c>
       <c r="K56" t="n">
-        <v>1.866562863105081e-05</v>
+        <v>0.002884247478418404</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2380045351473923</v>
+        <v>4.543636976191898e-05</v>
       </c>
       <c r="M56" t="n">
-        <v>1389.515625</v>
+        <v>0.2319954648526077</v>
+      </c>
+      <c r="N56" t="n">
+        <v>379.0415649414062</v>
       </c>
     </row>
     <row r="57">
@@ -2977,42 +3147,45 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8309.124755859375</v>
+        <v>2225.994873046875</v>
       </c>
       <c r="E57" t="n">
-        <v>1473.649243969836</v>
+        <v>2226</v>
       </c>
       <c r="F57" t="n">
-        <v>6.188673143888594</v>
+        <v>629.108278892135</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1773531253012728</v>
+        <v>1.746337987911445</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0007448044560318469</v>
+        <v>0.2826189253666296</v>
       </c>
       <c r="I57" t="n">
-        <v>1.012256512012363</v>
+        <v>0.0007845202201751301</v>
       </c>
       <c r="J57" t="n">
-        <v>0.003366944908550142</v>
+        <v>0.8526679083813181</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0002343120579684908</v>
+        <v>0.002078851578989388</v>
       </c>
       <c r="L57" t="n">
-        <v>0.47</v>
+        <v>8.941861024063079e-05</v>
       </c>
       <c r="M57" t="n">
-        <v>3905.288635253906</v>
+        <v>0.7449886621315193</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1658.340942382812</v>
       </c>
     </row>
     <row r="58">
@@ -3022,42 +3195,45 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LSrearSOAEwf1.mat</t>
+          <t>TH13RearwaveformSOAE.mat</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>732.12890625</v>
+        <v>904.39453125</v>
       </c>
       <c r="E58" t="n">
-        <v>431.1704675750619</v>
+        <v>904</v>
       </c>
       <c r="F58" t="n">
-        <v>1.367336064577971</v>
+        <v>343.030270228442</v>
       </c>
       <c r="G58" t="n">
-        <v>0.58892698252216</v>
+        <v>1.031354580719822</v>
       </c>
       <c r="H58" t="n">
-        <v>0.001867616553458507</v>
+        <v>0.379292729417908</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5639010890242845</v>
+        <v>0.001140381266231614</v>
       </c>
       <c r="J58" t="n">
-        <v>0.001380781937940807</v>
+        <v>0.5598673375450792</v>
       </c>
       <c r="K58" t="n">
-        <v>9.159737506708837e-05</v>
+        <v>0.001299316659547177</v>
       </c>
       <c r="L58" t="n">
-        <v>1.177006802721088</v>
+        <v>5.640480928701637e-05</v>
       </c>
       <c r="M58" t="n">
-        <v>861.720703125</v>
+        <v>0.7849886621315193</v>
+      </c>
+      <c r="N58" t="n">
+        <v>709.939453125</v>
       </c>
     </row>
     <row r="59">
@@ -3067,42 +3243,45 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LSrearSOAEwf1.mat</t>
+          <t>TH13RearwaveformSOAE.mat</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>985.14404296875</v>
+        <v>1520.782470703125</v>
       </c>
       <c r="E59" t="n">
-        <v>709.1199832076535</v>
+        <v>1521</v>
       </c>
       <c r="F59" t="n">
-        <v>3.402689580214135</v>
+        <v>715.2987461386782</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7198135016588104</v>
+        <v>1.302984173053143</v>
       </c>
       <c r="H59" t="n">
-        <v>0.003454002086801506</v>
+        <v>0.470349152438589</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4873676662189558</v>
+        <v>0.0008567853707905484</v>
       </c>
       <c r="J59" t="n">
-        <v>0.001619950741801077</v>
+        <v>0.7998867419989614</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0002302671668819459</v>
+        <v>0.001100296651841886</v>
       </c>
       <c r="L59" t="n">
-        <v>1.368004535147392</v>
+        <v>6.253134732348221e-05</v>
       </c>
       <c r="M59" t="n">
-        <v>1347.681518554688</v>
+        <v>1.033990929705215</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1572.475280761719</v>
       </c>
     </row>
     <row r="60">
@@ -3112,267 +3291,45 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LSrearSOAEwf1.mat</t>
+          <t>TH13RearwaveformSOAE.mat</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1633.831787109375</v>
+        <v>2037.579345703125</v>
       </c>
       <c r="E60" t="n">
-        <v>135.2652096623919</v>
+        <v>2038</v>
       </c>
       <c r="F60" t="n">
-        <v>1.034008662370157</v>
+        <v>392.3220091693045</v>
       </c>
       <c r="G60" t="n">
-        <v>0.08279016893269485</v>
+        <v>0.800818787024311</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0006328733903503964</v>
+        <v>0.1925431812001032</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4136555602514778</v>
+        <v>0.0003930245900426349</v>
       </c>
       <c r="J60" t="n">
-        <v>0.002884247478418404</v>
+        <v>0.9482389353904473</v>
       </c>
       <c r="K60" t="n">
-        <v>4.543636976191898e-05</v>
+        <v>0.001576792059309224</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2319954648526077</v>
+        <v>4.369121496770243e-05</v>
       </c>
       <c r="M60" t="n">
-        <v>379.0415649414062</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LSrearSOAEwf1.mat</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2225.994873046875</v>
-      </c>
-      <c r="E61" t="n">
-        <v>629.108278892135</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1.746337987911445</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.2826189253666296</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.0007845202201751301</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.8526679083813181</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.002078851578989388</v>
-      </c>
-      <c r="K61" t="n">
-        <v>8.941861024063079e-05</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.7449886621315193</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1658.340942382812</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>904.39453125</v>
-      </c>
-      <c r="E62" t="n">
-        <v>343.030270228442</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.031354580719822</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.379292729417908</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.001140381266231614</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.5598673375450792</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.001299316659547177</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.640480928701637e-05</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0.7849886621315193</v>
-      </c>
-      <c r="M62" t="n">
-        <v>709.939453125</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1520.782470703125</v>
-      </c>
-      <c r="E63" t="n">
-        <v>715.2987461386782</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.302984173053143</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.470349152438589</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.0008567853707905484</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.7998867419989614</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.001100296651841886</v>
-      </c>
-      <c r="K63" t="n">
-        <v>6.253134732348221e-05</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1.033990929705215</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1572.475280761719</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2037.579345703125</v>
-      </c>
-      <c r="E64" t="n">
-        <v>392.3220091693045</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.800818787024311</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.1925431812001032</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.0003930245900426349</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.9482389353904473</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.001576792059309224</v>
-      </c>
-      <c r="K64" t="n">
-        <v>4.369121496770243e-05</v>
-      </c>
-      <c r="L64" t="n">
         <v>0.4670068027210884</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N60" t="n">
         <v>951.5634155273438</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2694.342041015625</v>
-      </c>
-      <c r="E65" t="n">
-        <v>68.19075808329735</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1.613992291358184</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.02530887209019425</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.0005990302147198036</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.5452905533345958</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.01437082501153544</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0.00014404398542887</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.07700680272108844</v>
-      </c>
-      <c r="M65" t="n">
-        <v>207.482666015625</v>
       </c>
     </row>
   </sheetData>
